--- a/input/tam thoi/ott.xlsx
+++ b/input/tam thoi/ott.xlsx
@@ -1,28 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SkyTam\Desktop\cham-cong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup\cham-cong\input\tam thoi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028F1AB5-6D1E-489A-B5D9-F9234658F67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
-    <sheet name="20220118" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Tăng ca</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
+  <si>
+    <t>Công ty TNHH Sản Xuất Hiệp Phước Thành</t>
   </si>
   <si>
     <t>Mã nhân viên</t>
@@ -52,19 +56,92 @@
     <t>Trạng thái phê duyệt</t>
   </si>
   <si>
-    <t>Công ty TNHH Sản Xuất Hiệp Phước Thành</t>
+    <t>A068</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Phúc</t>
+  </si>
+  <si>
+    <t>BT Gia Công</t>
+  </si>
+  <si>
+    <t>Xin làm thêm</t>
+  </si>
+  <si>
+    <t>2022-04-29 06:00:00</t>
+  </si>
+  <si>
+    <t>2022-04-29 18:00:00</t>
+  </si>
+  <si>
+    <t>THAY THẾ 3 HỒ -PALADI-HCL-HỒ KHỬ NẤU LINE 1-1/XƯỞNG 1</t>
+  </si>
+  <si>
+    <t>2022-04-26 10:50:24</t>
+  </si>
+  <si>
+    <t>Phê duyệt</t>
+  </si>
+  <si>
+    <t>2022-04-24 06:00:00</t>
+  </si>
+  <si>
+    <t>2022-04-24 18:00:00</t>
+  </si>
+  <si>
+    <t>công việc ,gia công hồ cho line 1-1 còn 2 cái -gia công màng che line 2-1b2</t>
+  </si>
+  <si>
+    <t>2022-04-23 09:24:04</t>
+  </si>
+  <si>
+    <t>2022-04-17 06:00:00</t>
+  </si>
+  <si>
+    <t>2022-04-18 00:00:00</t>
+  </si>
+  <si>
+    <t>Sơn tường mặt trước toilet ,chổ qc xưởng 2 +ốp u nhựa hồ đánh than line 2-1b2 xưởng 2</t>
+  </si>
+  <si>
+    <t>2022-04-16 14:02:26</t>
+  </si>
+  <si>
+    <t>2022-04-10 06:00:00</t>
+  </si>
+  <si>
+    <t>2022-04-10 14:00:00</t>
+  </si>
+  <si>
+    <t>Sơn tường xung quanh tầng trệt xưởng 2</t>
+  </si>
+  <si>
+    <t>2022-04-09 06:32:20</t>
+  </si>
+  <si>
+    <t>2022-04-03 06:00:00</t>
+  </si>
+  <si>
+    <t>2022-04-03 18:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca ,lắp ráp thay mới hồ crom 6 ,hồ satin ,line 2-1b1</t>
+  </si>
+  <si>
+    <t>2022-03-31 08:50:13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,23 +204,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -156,7 +237,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -166,44 +247,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -231,31 +312,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -283,23 +347,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -311,212 +358,210 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" customWidth="1"/>
-    <col min="6" max="6" width="36.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
-    <col min="8" max="8" width="34.7109375" customWidth="1"/>
-    <col min="9" max="9" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="75.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5">
+        <v>6</v>
+      </c>
+      <c r="H2" s="5">
+        <v>7</v>
+      </c>
+      <c r="I2" s="5">
+        <v>8</v>
+      </c>
+      <c r="J2" s="5">
+        <v>9</v>
+      </c>
+      <c r="K2" s="5">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -529,7 +574,7 @@
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -545,34 +590,185 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>0.75</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>0.33333333333575865</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>0.5</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>